--- a/jira_export_2026-09-03.xlsx
+++ b/jira_export_2026-09-03.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>53 h</t>
+          <t>66 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P79"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -1542,32 +1542,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -1577,28 +1577,28 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
@@ -1614,12 +1614,12 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1629,12 +1629,12 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -1654,29 +1654,29 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="12" t="n">
@@ -1686,27 +1686,27 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -1726,21 +1726,29 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr"/>
-      <c r="M14" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M14" s="14" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="15" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O14" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
@@ -1750,27 +1758,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1780,7 +1788,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1797,22 +1805,14 @@
         <v>3</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr"/>
+      <c r="M15" s="11" t="inlineStr"/>
       <c r="N15" s="12" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O15" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1822,32 +1822,32 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1857,32 +1857,32 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J16" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M16" s="14" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N16" s="15" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O16" s="16" t="n">
         <v>0</v>
@@ -1894,32 +1894,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1966,12 +1966,12 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
@@ -2013,20 +2013,20 @@
         <v>3</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2038,27 +2038,27 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2073,32 +2073,32 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J19" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2110,12 +2110,12 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
@@ -2161,16 +2161,16 @@
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2182,12 +2182,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2233,16 +2233,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2254,27 +2254,27 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2305,16 +2305,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2326,32 +2326,32 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2398,27 +2398,27 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -2445,20 +2445,20 @@
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2470,12 +2470,12 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2510,29 +2510,29 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="O25" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P25" s="12" t="n">
@@ -2542,12 +2542,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2589,22 +2589,22 @@
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2614,27 +2614,27 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2654,27 +2654,27 @@
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2686,27 +2686,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2726,27 +2726,27 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>171.4</v>
+        <v>920</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2758,32 +2758,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2809,16 +2809,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2830,27 +2830,27 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2881,16 +2881,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2902,27 +2902,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2953,16 +2953,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,32 +3046,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3097,16 +3097,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,12 +3118,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -3158,27 +3158,27 @@
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K34" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3190,32 +3190,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3225,32 +3225,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3262,27 +3262,27 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3302,29 +3302,29 @@
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="O36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
@@ -3334,12 +3334,12 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3374,29 +3374,29 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3406,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3441,32 +3441,32 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K38" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O38" s="16" t="n">
         <v>0</v>
@@ -3478,32 +3478,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,34 +3513,34 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="12" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O39" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P39" s="12" t="n">
@@ -3550,32 +3550,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,34 +3585,34 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>450</v>
-      </c>
-      <c r="O40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
@@ -3622,32 +3622,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3694,32 +3694,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3729,32 +3729,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,12 +3766,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3801,12 +3801,12 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -3817,16 +3817,16 @@
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3838,32 +3838,32 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3878,27 +3878,27 @@
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3910,12 +3910,12 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3982,32 +3982,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -4033,16 +4033,16 @@
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4054,27 +4054,27 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4089,32 +4089,32 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,12 +4126,12 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
@@ -4177,16 +4177,16 @@
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4198,32 +4198,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4270,32 +4270,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4321,16 +4321,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4342,12 +4342,12 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4393,16 +4393,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,12 +4414,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4465,16 +4465,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4486,12 +4486,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,27 +4526,27 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4558,32 +4558,32 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4630,27 +4630,27 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -4670,27 +4670,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4753,16 +4753,16 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4774,32 +4774,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4809,35 +4809,35 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
@@ -4846,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4881,35 +4881,35 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P58" s="15" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>10</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
@@ -5037,16 +5037,16 @@
         <v>10</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
@@ -5109,16 +5109,16 @@
         <v>10</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
@@ -5181,22 +5181,22 @@
         <v>10</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5206,12 +5206,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5221,11 +5221,13 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
         <is>
@@ -5239,12 +5241,12 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5255,18 +5257,18 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="12" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O63" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5276,12 +5278,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5291,34 +5293,48 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="14" t="inlineStr"/>
-      <c r="M64" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L64" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M64" s="14" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N64" s="15" t="n">
         <v>0</v>
       </c>
@@ -5332,12 +5348,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5347,48 +5363,34 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v/>
-      </c>
-      <c r="F65" s="11" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr"/>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M65" s="11" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr"/>
       <c r="N65" s="12" t="n">
         <v>0</v>
       </c>
@@ -5402,12 +5404,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5417,7 +5419,7 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E66" s="14" t="n">
@@ -5435,34 +5437,34 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5472,12 +5474,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5487,7 +5489,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5510,29 +5512,29 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="12" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O67" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5542,22 +5544,22 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
@@ -5575,34 +5577,34 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5612,12 +5614,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5627,7 +5629,7 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5645,34 +5647,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5682,12 +5684,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5697,7 +5699,7 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E70" s="14" t="n">
@@ -5715,34 +5717,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>17</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O70" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5752,22 +5754,22 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5780,7 +5782,7 @@
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5790,21 +5792,29 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr"/>
-      <c r="M71" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O71" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5814,22 +5824,22 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E72" s="14" t="n">
@@ -5847,7 +5857,7 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
@@ -5859,7 +5869,7 @@
         <v>21</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L72" s="14" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -5876,22 +5886,22 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5899,44 +5909,36 @@
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>21</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M73" s="11" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr"/>
       <c r="N73" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O73" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5946,22 +5948,22 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -5969,7 +5971,7 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -5979,12 +5981,12 @@
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
@@ -5995,16 +5997,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6016,22 +6018,22 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -6044,31 +6046,39 @@
       </c>
       <c r="G75" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L75" s="11" t="inlineStr"/>
-      <c r="M75" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O75" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P75" s="12" t="n">
@@ -6078,22 +6088,22 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6106,35 +6116,27 @@
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K76" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L76" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M76" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+      <c r="L76" s="14" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
       <c r="N76" s="15" t="n">
         <v>0</v>
       </c>
@@ -6148,22 +6150,22 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6176,23 +6178,35 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H77" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
@@ -6206,24 +6220,26 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C78" s="14" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n">
+        <v/>
       </c>
       <c r="F78" s="14" t="inlineStr">
         <is>
@@ -6235,21 +6251,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H78" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H78" s="14" t="inlineStr"/>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L78" s="14" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -6264,31 +6276,91 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr"/>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K79" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr"/>
+      <c r="N79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr"/>
-      <c r="C79" s="17" t="inlineStr"/>
-      <c r="D79" s="17" t="inlineStr"/>
-      <c r="E79" s="17" t="inlineStr"/>
-      <c r="F79" s="17" t="inlineStr"/>
-      <c r="G79" s="17" t="inlineStr"/>
-      <c r="H79" s="17" t="inlineStr"/>
-      <c r="I79" s="17" t="inlineStr"/>
-      <c r="J79" s="17" t="inlineStr"/>
-      <c r="K79" s="17" t="inlineStr"/>
-      <c r="L79" s="17" t="inlineStr"/>
-      <c r="M79" s="17" t="inlineStr"/>
-      <c r="N79" s="18" t="n">
+      <c r="B80" s="17" t="inlineStr"/>
+      <c r="C80" s="17" t="inlineStr"/>
+      <c r="D80" s="17" t="inlineStr"/>
+      <c r="E80" s="17" t="inlineStr"/>
+      <c r="F80" s="17" t="inlineStr"/>
+      <c r="G80" s="17" t="inlineStr"/>
+      <c r="H80" s="17" t="inlineStr"/>
+      <c r="I80" s="17" t="inlineStr"/>
+      <c r="J80" s="17" t="inlineStr"/>
+      <c r="K80" s="17" t="inlineStr"/>
+      <c r="L80" s="17" t="inlineStr"/>
+      <c r="M80" s="17" t="inlineStr"/>
+      <c r="N80" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O79" s="18" t="n">
+      <c r="O80" s="18" t="n">
         <v>1265.22</v>
       </c>
-      <c r="P79" s="18" t="n">
-        <v>40.81</v>
+      <c r="P80" s="18" t="n">
+        <v>35.89</v>
       </c>
     </row>
   </sheetData>
@@ -6368,6 +6440,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6379,18 +6452,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
@@ -6405,7 +6478,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 0 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 1 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -6467,8 +6540,83 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-35000</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE PALAVAS-LES-FLOTS] - Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE PALAVAS-LES-FLOTS</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Ajout d'un Pax + Carte M2M + reinst apk et cb</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35006</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>00178435</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr"/>
+      <c r="C6" s="17" t="inlineStr"/>
+      <c r="D6" s="17" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr"/>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="17" t="inlineStr"/>
+      <c r="H6" s="17" t="inlineStr"/>
+      <c r="I6" s="17" t="inlineStr"/>
+      <c r="J6" s="17" t="inlineStr"/>
+      <c r="K6" s="18" t="n">
+        <v>815</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A4:K4"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6942,26 +7090,26 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>15.25</v>
+        <v>17.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>4.75</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>21.5</v>
+        <v>25.75</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>652.05</v>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7132,7 @@
         <v>8.5</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" s="11" t="n">
         <v>275.31</v>
@@ -7003,7 +7151,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>17.25</v>
+        <v>23.5</v>
       </c>
     </row>
   </sheetData>
@@ -7088,10 +7236,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>365120</v>
+        <v>369094</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>133030</v>
+        <v>137004</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>232090</v>
@@ -7113,10 +7261,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>163380</v>
+        <v>167354</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>59733</v>
+        <v>63707</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>103647</v>
@@ -7167,15 +7315,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -7191,7 +7339,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 2 commande(s)</t>
+          <t>Épics créées ce mois — 3 commande(s)</t>
         </is>
       </c>
     </row>
@@ -7334,30 +7482,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
-      <c r="E7" s="17" t="n"/>
-      <c r="F7" s="17" t="n"/>
-      <c r="G7" s="17" t="n"/>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>2 commande(s)</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="n">
-        <v>1200</v>
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35439</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35435</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2026</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>00180506</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>3974</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B8" s="17" t="n"/>
@@ -7368,17 +7540,17 @@
       <c r="G8" s="17" t="n"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>0 commande(s)</t>
+          <t>3 commande(s)</t>
         </is>
       </c>
       <c r="I8" s="24" t="n">
-        <v>0</v>
+        <v>5174</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B9" s="17" t="n"/>
@@ -7389,10 +7561,31 @@
       <c r="G9" s="17" t="n"/>
       <c r="H9" s="17" t="inlineStr">
         <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="n">
+        <v>3974</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
           <t>2 commande(s)</t>
         </is>
       </c>
-      <c r="I9" s="24" t="n">
+      <c r="I10" s="24" t="n">
         <v>1200</v>
       </c>
     </row>

--- a/jira_export_2026-09-03.xlsx
+++ b/jira_export_2026-09-03.xlsx
@@ -720,7 +720,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>1,265 €</t>
+          <t>1,805 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -734,7 +734,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -760,7 +760,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>903 €</t>
+          <t>1,443 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>66 h</t>
+          <t>68 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -900,7 +900,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1237,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -1941,7 +1941,7 @@
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
@@ -2758,12 +2758,12 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2773,12 +2773,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2798,64 +2798,64 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O29" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O29" s="12" t="n">
+        <v>540</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2881,16 +2881,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2902,27 +2902,27 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2953,16 +2953,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,27 +2974,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,32 +3046,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3097,16 +3097,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3190,12 +3190,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
@@ -3230,27 +3230,27 @@
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1207</v>
+        <v>910</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3262,32 +3262,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>500</v>
+        <v>1207</v>
       </c>
       <c r="O36" s="16" t="n">
         <v>0</v>
@@ -3334,27 +3334,27 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
@@ -3374,29 +3374,29 @@
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3406,12 +3406,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -3446,29 +3446,29 @@
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3478,32 +3478,32 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
@@ -3513,32 +3513,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3550,32 +3550,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,34 +3585,34 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="15" t="n">
+        <v>2335</v>
+      </c>
+      <c r="O40" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
@@ -3622,32 +3622,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3657,34 +3657,34 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -3694,32 +3694,32 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3729,32 +3729,32 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K42" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,32 +3766,32 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G43" s="11" t="inlineStr">
@@ -3801,32 +3801,32 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>590.15</v>
+        <v>910</v>
       </c>
       <c r="O43" s="16" t="n">
         <v>0</v>
@@ -3838,12 +3838,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3889,16 +3889,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>285</v>
+        <v>590.15</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3910,32 +3910,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3982,12 +3982,12 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -4022,27 +4022,27 @@
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4054,32 +4054,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4105,16 +4105,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,27 +4126,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4161,32 +4161,32 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K48" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4198,12 +4198,12 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4249,16 +4249,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4270,32 +4270,32 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4321,16 +4321,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4342,32 +4342,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4393,16 +4393,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>210</v>
+        <v>700</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,12 +4414,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4465,16 +4465,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4486,12 +4486,12 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4537,16 +4537,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4558,12 +4558,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4598,27 +4598,27 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K54" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4630,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4665,32 +4665,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>8</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4702,27 +4702,27 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4742,27 +4742,27 @@
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>187.5</v>
+        <v>690</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4825,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,32 +4846,32 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -4881,35 +4881,35 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K58" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="15" t="n">
-        <v>362.5</v>
+        <v>787.5</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4953,35 +4953,35 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
@@ -5041,12 +5041,12 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
@@ -5113,12 +5113,12 @@
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
@@ -5257,18 +5257,18 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P63" s="12" t="n">
@@ -5278,12 +5278,12 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
@@ -5293,11 +5293,13 @@
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
@@ -5311,12 +5313,12 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J64" s="14" t="n">
@@ -5327,18 +5329,18 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O64" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5348,12 +5350,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5363,34 +5365,48 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F65" s="11" t="inlineStr"/>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F65" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G65" s="11" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H65" s="11" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H65" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="11" t="inlineStr"/>
-      <c r="M65" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27642</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>00143935</t>
+        </is>
+      </c>
       <c r="N65" s="12" t="n">
         <v>0</v>
       </c>
@@ -5404,12 +5420,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5419,48 +5435,34 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E66" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E66" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr"/>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr"/>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L66" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-26814</t>
-        </is>
-      </c>
-      <c r="M66" s="14" t="inlineStr">
-        <is>
-          <t>00142941</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
       <c r="N66" s="15" t="n">
         <v>0</v>
       </c>
@@ -5474,12 +5476,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5489,7 +5491,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5507,34 +5509,34 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O67" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P67" s="12" t="n">
@@ -5544,12 +5546,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5559,7 +5561,7 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E68" s="14" t="n">
@@ -5582,29 +5584,29 @@
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5614,22 +5616,22 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5647,34 +5649,34 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>401</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5684,12 +5686,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5699,7 +5701,7 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E70" s="14" t="n">
@@ -5717,34 +5719,34 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="O70" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P70" s="15" t="n">
@@ -5754,12 +5756,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5769,7 +5771,7 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5787,34 +5789,34 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5824,22 +5826,22 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E72" s="14" t="n">
@@ -5852,7 +5854,7 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -5862,21 +5864,29 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L72" s="14" t="inlineStr"/>
-      <c r="M72" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L72" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M72" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N72" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O72" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5886,22 +5896,22 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5919,7 +5929,7 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
@@ -5931,7 +5941,7 @@
         <v>21</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="L73" s="11" t="inlineStr"/>
       <c r="M73" s="11" t="inlineStr"/>
@@ -5948,22 +5958,22 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -5971,44 +5981,36 @@
       </c>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
         <v>21</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M74" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L74" s="14" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
       <c r="N74" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O74" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P74" s="15" t="n">
@@ -6018,22 +6020,22 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -6041,7 +6043,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6051,12 +6053,12 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
@@ -6067,16 +6069,16 @@
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6088,22 +6090,22 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6116,31 +6118,39 @@
       </c>
       <c r="G76" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L76" s="14" t="inlineStr"/>
-      <c r="M76" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L76" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M76" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6150,22 +6160,22 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13128</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6178,35 +6188,27 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/10/2023</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L77" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M77" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr"/>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
@@ -6220,22 +6222,22 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
@@ -6248,23 +6250,35 @@
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H78" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H78" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
         <v>36</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr"/>
-      <c r="M78" s="14" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M78" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N78" s="15" t="n">
         <v>0</v>
       </c>
@@ -6278,24 +6292,26 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr"/>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v/>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
@@ -6307,21 +6323,17 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H79" s="11" t="inlineStr"/>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
         <v>36</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
@@ -6336,31 +6348,91 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="inlineStr">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr"/>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K80" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+      <c r="N80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B80" s="17" t="inlineStr"/>
-      <c r="C80" s="17" t="inlineStr"/>
-      <c r="D80" s="17" t="inlineStr"/>
-      <c r="E80" s="17" t="inlineStr"/>
-      <c r="F80" s="17" t="inlineStr"/>
-      <c r="G80" s="17" t="inlineStr"/>
-      <c r="H80" s="17" t="inlineStr"/>
-      <c r="I80" s="17" t="inlineStr"/>
-      <c r="J80" s="17" t="inlineStr"/>
-      <c r="K80" s="17" t="inlineStr"/>
-      <c r="L80" s="17" t="inlineStr"/>
-      <c r="M80" s="17" t="inlineStr"/>
-      <c r="N80" s="18" t="n">
+      <c r="B81" s="17" t="inlineStr"/>
+      <c r="C81" s="17" t="inlineStr"/>
+      <c r="D81" s="17" t="inlineStr"/>
+      <c r="E81" s="17" t="inlineStr"/>
+      <c r="F81" s="17" t="inlineStr"/>
+      <c r="G81" s="17" t="inlineStr"/>
+      <c r="H81" s="17" t="inlineStr"/>
+      <c r="I81" s="17" t="inlineStr"/>
+      <c r="J81" s="17" t="inlineStr"/>
+      <c r="K81" s="17" t="inlineStr"/>
+      <c r="L81" s="17" t="inlineStr"/>
+      <c r="M81" s="17" t="inlineStr"/>
+      <c r="N81" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O80" s="18" t="n">
-        <v>1265.22</v>
-      </c>
-      <c r="P80" s="18" t="n">
-        <v>35.89</v>
+      <c r="O81" s="18" t="n">
+        <v>1805.22</v>
+      </c>
+      <c r="P81" s="18" t="n">
+        <v>49.12</v>
       </c>
     </row>
   </sheetData>
@@ -6441,6 +6513,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7090,16 +7163,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>17.75</v>
+        <v>18.75</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>4.75</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>25.75</v>
+        <v>27.25</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>3.5</v>
@@ -7109,7 +7182,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -7236,16 +7309,16 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>369094</v>
+        <v>368554</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>137004</v>
+        <v>128054</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>232090</v>
+        <v>240501</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>144874</v>
+        <v>144334</v>
       </c>
       <c r="F5" s="24" t="n">
         <v>21179</v>
@@ -7261,16 +7334,16 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>167354</v>
+        <v>166814</v>
       </c>
       <c r="C6" s="25" t="n">
         <v>63707</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>103647</v>
+        <v>103107</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>86630</v>
+        <v>86090</v>
       </c>
       <c r="F6" s="25" t="n">
         <v>11307</v>
@@ -7289,10 +7362,10 @@
         <v>201740</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>73297</v>
+        <v>64347</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>128443</v>
+        <v>137393</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>58244</v>

--- a/jira_export_2026-09-03.xlsx
+++ b/jira_export_2026-09-03.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>68 h</t>
+          <t>74 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P81"/>
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1054,27 +1054,27 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35184</t>
+          <t>PDMDEP-35435</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
+          <t>[CD 92] - Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Marine MASINGARBE</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAILLARD</t>
+          <t>DEPARTEMENT DES HAUTS-DE-SEINE</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Prestation forfait - Reprise de charte graphique</t>
+          <t>Modélisation suite audit sur site</t>
         </is>
       </c>
       <c r="F5" s="11" t="inlineStr">
@@ -1094,59 +1094,59 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>21/08/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="J5" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35188</t>
+          <t>PDMDEP-35439</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
-          <t>00178947</t>
+          <t>00180506</t>
         </is>
       </c>
       <c r="N5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>902.72</v>
+        <v>0</v>
       </c>
       <c r="P5" s="12" t="n">
-        <v>451.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35037</t>
+          <t>PDMDEP-35184</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>[COMMUNE DE GAILLARD] - Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Marine MASINGARBE</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
+          <t>COMMUNE DE GAILLARD</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
+          <t>Prestation forfait - Reprise de charte graphique</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
@@ -1166,36 +1166,44 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>21/08/2026</t>
         </is>
       </c>
       <c r="J6" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L6" s="14" t="inlineStr"/>
-      <c r="M6" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35188</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>00178947</t>
+        </is>
+      </c>
       <c r="N6" s="15" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0</v>
+        <v>902.72</v>
       </c>
       <c r="P6" s="15" t="n">
-        <v>0</v>
+        <v>451.36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35029</t>
+          <t>PDMDEP-35037</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
+          <t xml:space="preserve">[VILLE DE VILLEFRANCHE SUR SAONE ] - mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1205,12 +1213,12 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE LEVALLOIS PERRET</t>
+          <t xml:space="preserve">VILLE DE VILLEFRANCHE SUR SAONE </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hébergement Litt Exp </t>
+          <t xml:space="preserve">mise a jour carto comprise dans leur abonnement annuel </t>
         </is>
       </c>
       <c r="F7" s="11" t="inlineStr">
@@ -1220,7 +1228,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -1237,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>3.5</v>
+        <v>0.25</v>
       </c>
       <c r="L7" s="11" t="inlineStr"/>
       <c r="M7" s="11" t="inlineStr"/>
@@ -1254,27 +1262,27 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35029</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[VILLE DE LEVALLOIS PERRET] - Hébergement Litt Exp test et prod</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>VILLE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t xml:space="preserve">Hébergement Litt Exp </t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1284,7 +1292,7 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -1294,29 +1302,21 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34979</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="inlineStr">
-        <is>
-          <t>00178226</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
       <c r="N8" s="15" t="n">
-        <v>1100</v>
-      </c>
-      <c r="O8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="15" t="n">
@@ -1326,32 +1326,32 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier et ODP</t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -1361,32 +1361,32 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N9" s="12" t="n">
-        <v>2419</v>
+        <v>1100</v>
       </c>
       <c r="O9" s="16" t="n">
         <v>0</v>
@@ -1398,27 +1398,27 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[Ville de Bourges] - Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>Migration GEODP Placier et ODP</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
@@ -1445,22 +1445,22 @@
         <v>2</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="M10" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="N10" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="15" t="n">
+        <v>2419</v>
+      </c>
+      <c r="O10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P10" s="15" t="n">
@@ -1470,32 +1470,32 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F11" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1505,34 +1505,34 @@
       </c>
       <c r="H11" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1260</v>
-      </c>
-      <c r="O11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P11" s="12" t="n">
@@ -1542,12 +1542,12 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -1582,29 +1582,29 @@
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J12" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M12" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="15" t="n">
+        <v>1260</v>
+      </c>
+      <c r="O12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P12" s="15" t="n">
@@ -1614,32 +1614,32 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34411</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE MAIZIERES LES METZ</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1649,28 +1649,28 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J13" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34420</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>00172317</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N13" s="12" t="n">
@@ -1686,12 +1686,12 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34411</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t>[MAIRIE DE MAIZIERES LES METZ] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>MAIRIE DE MAIZIERES LES METZ</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -1726,29 +1726,29 @@
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/07/2026</t>
         </is>
       </c>
       <c r="J14" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34420</t>
         </is>
       </c>
       <c r="M14" s="14" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172317</t>
         </is>
       </c>
       <c r="N14" s="15" t="n">
-        <v>769.5</v>
-      </c>
-      <c r="O14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P14" s="15" t="n">
@@ -1758,27 +1758,27 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1798,21 +1798,29 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J15" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34326</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>00171691</t>
+        </is>
+      </c>
       <c r="N15" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="12" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="O15" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P15" s="12" t="n">
@@ -1822,27 +1830,27 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -1852,7 +1860,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -1869,22 +1877,14 @@
         <v>3</v>
       </c>
       <c r="K16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L16" s="14" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
       <c r="N16" s="15" t="n">
-        <v>2127.2</v>
-      </c>
-      <c r="O16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="15" t="n">
@@ -1894,32 +1894,32 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J17" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N17" s="12" t="n">
-        <v>4536</v>
+        <v>2127.2</v>
       </c>
       <c r="O17" s="16" t="n">
         <v>0</v>
@@ -1966,32 +1966,32 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J18" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K18" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M18" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N18" s="15" t="n">
-        <v>525</v>
+        <v>4536</v>
       </c>
       <c r="O18" s="16" t="n">
         <v>0</v>
@@ -2038,12 +2038,12 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
@@ -2085,20 +2085,20 @@
         <v>3</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1662</v>
+        <v>525</v>
       </c>
       <c r="O19" s="16" t="n">
         <v>0</v>
@@ -2110,27 +2110,27 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -2145,32 +2145,32 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J20" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K20" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M20" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>9623.1</v>
+        <v>1662</v>
       </c>
       <c r="O20" s="16" t="n">
         <v>0</v>
@@ -2182,12 +2182,12 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34108</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + migration ODP</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J21" s="11" t="n">
@@ -2233,16 +2233,16 @@
       </c>
       <c r="L21" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34117</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>00170907</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N21" s="12" t="n">
-        <v>707</v>
+        <v>9623.1</v>
       </c>
       <c r="O21" s="16" t="n">
         <v>0</v>
@@ -2254,12 +2254,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34108</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DU PUY EN VELAY] - Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GeODP Placier + migration ODP</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -2289,12 +2289,12 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="J22" s="14" t="n">
@@ -2305,16 +2305,16 @@
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34117</t>
         </is>
       </c>
       <c r="M22" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170907</t>
         </is>
       </c>
       <c r="N22" s="15" t="n">
-        <v>300</v>
+        <v>707</v>
       </c>
       <c r="O22" s="16" t="n">
         <v>0</v>
@@ -2326,27 +2326,27 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J23" s="11" t="n">
@@ -2377,16 +2377,16 @@
       </c>
       <c r="L23" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N23" s="12" t="n">
-        <v>510</v>
+        <v>300</v>
       </c>
       <c r="O23" s="16" t="n">
         <v>0</v>
@@ -2398,32 +2398,32 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2433,32 +2433,32 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J24" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K24" s="14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M24" s="14" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N24" s="15" t="n">
-        <v>242.9</v>
+        <v>510</v>
       </c>
       <c r="O24" s="16" t="n">
         <v>0</v>
@@ -2470,27 +2470,27 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -2517,20 +2517,20 @@
         <v>3</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N25" s="12" t="n">
-        <v>220</v>
+        <v>242.9</v>
       </c>
       <c r="O25" s="16" t="n">
         <v>0</v>
@@ -2542,12 +2542,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2582,29 +2582,29 @@
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M26" s="14" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="15" t="n">
+        <v>220</v>
+      </c>
+      <c r="O26" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2614,12 +2614,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2661,22 +2661,22 @@
         <v>3</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1890</v>
-      </c>
-      <c r="O27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P27" s="12" t="n">
@@ -2686,27 +2686,27 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2726,27 +2726,27 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J28" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K28" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>920</v>
+        <v>1890</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2758,27 +2758,27 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33699</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2809,33 +2809,33 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33703</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00169363</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="12" t="n">
-        <v>540</v>
+        <v>920</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>1080</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33699</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t>[CD 35)] - Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t>DEPARTEMENT D'ILLE ET VILAINE (CD 35)</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t>Montée de version Littéralis - 1 journée d'assistance fonctionnelle à distance</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -2870,64 +2870,64 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33703</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00169363</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>171.4</v>
-      </c>
-      <c r="O30" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O30" s="15" t="n">
+        <v>540</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2953,16 +2953,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>344</v>
+        <v>171.4</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,27 +2974,27 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
@@ -3025,16 +3025,16 @@
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33272</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00166910</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>500</v>
+        <v>344</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,27 +3046,27 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3097,16 +3097,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>149</v>
+        <v>500</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>625</v>
+        <v>149</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3190,32 +3190,32 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33170</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Commune de Bonneville</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G35" s="11" t="inlineStr">
@@ -3225,32 +3225,32 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J35" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33177</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00166356</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>910</v>
+        <v>625</v>
       </c>
       <c r="O35" s="16" t="n">
         <v>0</v>
@@ -3262,32 +3262,32 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33064</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LONGWY</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -3297,34 +3297,34 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J36" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>2</v>
+        <v>0.12</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33073</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
         <is>
-          <t>00165708</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>1207</v>
-      </c>
-      <c r="O36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P36" s="15" t="n">
@@ -3334,32 +3334,32 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33170</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[Commune de Bonneville] - MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>Commune de Bonneville</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>MIGRATION GEODP PLACIER ON PREM VERS SAAS</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3369,32 +3369,32 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33177</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00166356</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>500</v>
+        <v>910</v>
       </c>
       <c r="O37" s="16" t="n">
         <v>0</v>
@@ -3406,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-33064</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[MAIRIE DE LONGWY] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>MAIRIE DE LONGWY</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3441,34 +3441,34 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="J38" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-33073</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00165708</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="15" t="n">
+        <v>1207</v>
+      </c>
+      <c r="O38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3478,27 +3478,27 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
@@ -3529,16 +3529,16 @@
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>142.1</v>
+        <v>500</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3550,32 +3550,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,34 +3585,34 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K40" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>2335</v>
-      </c>
-      <c r="O40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P40" s="15" t="n">
@@ -3622,27 +3622,27 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
@@ -3662,29 +3662,29 @@
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="12" t="n">
+        <v>142.1</v>
+      </c>
+      <c r="O41" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P41" s="12" t="n">
@@ -3694,27 +3694,27 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J42" s="14" t="n">
@@ -3745,16 +3745,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,12 +3766,12 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t>[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod  (03/26)</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3806,29 +3806,29 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="L43" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N43" s="12" t="n">
-        <v>910</v>
-      </c>
-      <c r="O43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -3838,12 +3838,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J44" s="14" t="n">
@@ -3889,16 +3889,16 @@
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N44" s="15" t="n">
-        <v>590.15</v>
+        <v>450</v>
       </c>
       <c r="O44" s="16" t="n">
         <v>0</v>
@@ -3910,32 +3910,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3950,27 +3950,27 @@
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>285</v>
+        <v>910</v>
       </c>
       <c r="O45" s="16" t="n">
         <v>0</v>
@@ -3982,32 +3982,32 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4017,32 +4017,32 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>1325</v>
+        <v>590.15</v>
       </c>
       <c r="O46" s="16" t="n">
         <v>0</v>
@@ -4054,32 +4054,32 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G47" s="11" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J47" s="11" t="n">
@@ -4105,16 +4105,16 @@
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4126,32 +4126,32 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -4161,32 +4161,32 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>588</v>
+        <v>1325</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4198,32 +4198,32 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
@@ -4233,32 +4233,32 @@
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>203.5</v>
+        <v>120</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4270,27 +4270,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4310,27 +4310,27 @@
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K50" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>300</v>
+        <v>588</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4342,32 +4342,32 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
@@ -4393,16 +4393,16 @@
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>700</v>
+        <v>203.5</v>
       </c>
       <c r="O51" s="16" t="n">
         <v>0</v>
@@ -4414,27 +4414,27 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
@@ -4465,16 +4465,16 @@
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>210</v>
+        <v>300</v>
       </c>
       <c r="O52" s="16" t="n">
         <v>0</v>
@@ -4486,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
@@ -4537,16 +4537,16 @@
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4558,12 +4558,12 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4609,16 +4609,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4630,12 +4630,12 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
@@ -4670,27 +4670,27 @@
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4702,32 +4702,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4737,32 +4737,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>690</v>
+        <v>255</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4774,32 +4774,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
@@ -4825,16 +4825,16 @@
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>187.5</v>
+        <v>140</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4846,27 +4846,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4886,27 +4886,27 @@
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>8</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>787.5</v>
+        <v>690</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4918,32 +4918,32 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G59" s="11" t="inlineStr">
@@ -4953,35 +4953,35 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>362.5</v>
+        <v>187.5</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
@@ -4990,27 +4990,27 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5025,34 +5025,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
+        <v>787.5</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5062,32 +5062,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>Commune de CLAMART</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>Déploiement Littéralis Expert</t>
+          <t>Migration V2</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5097,35 +5097,35 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O61" s="12" t="n">
-        <v>0</v>
+        <v>362.5</v>
       </c>
       <c r="P61" s="12" t="n">
         <v>0</v>
@@ -5181,16 +5181,16 @@
         <v>10</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
@@ -5253,16 +5253,16 @@
         <v>10</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
@@ -5325,22 +5325,22 @@
         <v>10</v>
       </c>
       <c r="K64" s="14" t="n">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P64" s="15" t="n">
@@ -5350,12 +5350,12 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
@@ -5365,11 +5365,13 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
-        </is>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
@@ -5383,28 +5385,28 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.5</v>
+        <v>1.05</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
@@ -5420,12 +5422,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5435,38 +5437,54 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>CD74</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr"/>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H66" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K66" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L66" s="14" t="inlineStr"/>
-      <c r="M66" s="14" t="inlineStr"/>
+        <v>1.05</v>
+      </c>
+      <c r="L66" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28202</t>
+        </is>
+      </c>
+      <c r="M66" s="14" t="inlineStr">
+        <is>
+          <t>00144857</t>
+        </is>
+      </c>
       <c r="N66" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O66" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P66" s="15" t="n">
@@ -5476,12 +5494,12 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
@@ -5491,7 +5509,7 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -5514,23 +5532,23 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>10</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
@@ -5546,12 +5564,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5561,52 +5579,38 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
-        </is>
-      </c>
-      <c r="E68" s="14" t="n">
-        <v/>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E68" s="14" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H68" s="14" t="inlineStr"/>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27017</t>
-        </is>
-      </c>
-      <c r="M68" s="14" t="inlineStr">
-        <is>
-          <t>00141205</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
       <c r="N68" s="15" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O68" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5616,12 +5620,12 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -5649,28 +5653,28 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
@@ -5686,22 +5690,22 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E70" s="14" t="n">
@@ -5719,32 +5723,32 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K70" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>401</v>
+        <v>1212</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5756,22 +5760,22 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -5794,23 +5798,23 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
@@ -5826,26 +5830,28 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-23750</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>MEL - LITTERALIS x AXION</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="n">
-        <v/>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>AXION</t>
+        </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
@@ -5854,7 +5860,7 @@
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H72" s="14" t="inlineStr">
@@ -5864,29 +5870,29 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>08/08/2025</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K72" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-27033</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>497304</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>230</v>
-      </c>
-      <c r="O72" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P72" s="15" t="n">
@@ -5896,22 +5902,22 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -5924,7 +5930,7 @@
       </c>
       <c r="G73" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -5934,21 +5940,29 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L73" s="11" t="inlineStr"/>
-      <c r="M73" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O73" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P73" s="12" t="n">
@@ -5958,12 +5972,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -5973,7 +5987,7 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E74" s="14" t="n">
@@ -5986,7 +6000,7 @@
       </c>
       <c r="G74" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr">
@@ -5996,17 +6010,25 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K74" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L74" s="14" t="inlineStr"/>
-      <c r="M74" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L74" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28036</t>
+        </is>
+      </c>
+      <c r="M74" s="14" t="inlineStr">
+        <is>
+          <t>483799</t>
+        </is>
+      </c>
       <c r="N74" s="15" t="n">
         <v>0</v>
       </c>
@@ -6020,22 +6042,22 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -6043,7 +6065,7 @@
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6053,32 +6075,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K75" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6090,22 +6112,22 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E76" s="14" t="n">
@@ -6123,34 +6145,34 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28215</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>557.145</v>
-      </c>
-      <c r="O76" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6160,12 +6182,12 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13128</t>
+          <t>PDMDEP-19558</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+          <t>[VILLEFONTAINE] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
@@ -6175,7 +6197,7 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>VILLEFONTAINE</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
@@ -6188,7 +6210,7 @@
       </c>
       <c r="G77" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H77" s="11" t="inlineStr">
@@ -6198,17 +6220,25 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>30/10/2023</t>
+          <t>28/02/2025</t>
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="K77" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L77" s="11" t="inlineStr"/>
-      <c r="M77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28214</t>
+        </is>
+      </c>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>458286</t>
+        </is>
+      </c>
       <c r="N77" s="12" t="n">
         <v>0</v>
       </c>
@@ -6222,22 +6252,22 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E78" s="14" t="n">
@@ -6250,7 +6280,7 @@
       </c>
       <c r="G78" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H78" s="14" t="inlineStr">
@@ -6260,25 +6290,17 @@
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K78" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L78" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M78" s="14" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L78" s="14" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
       <c r="N78" s="15" t="n">
         <v>0</v>
       </c>
@@ -6292,22 +6314,22 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
@@ -6323,17 +6345,21 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H79" s="11" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="L79" s="11" t="inlineStr"/>
       <c r="M79" s="11" t="inlineStr"/>
@@ -6350,89 +6376,419 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
+          <t>PDMDEP-18115</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
+        <is>
+          <t>BISCHWILLER</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="G80" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H80" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="I80" s="14" t="inlineStr">
+        <is>
+          <t>17/12/2024</t>
+        </is>
+      </c>
+      <c r="J80" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K80" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M80" s="14" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
+      <c r="N80" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="O80" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-18037</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>LE PERREUX SUR MARNE</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F81" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G81" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H81" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>12/12/2024</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K81" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O81" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-13128</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>[VALENCIENNES] Littéralis Prime - RAF FAST PARAPHEUR - Déjà facturé</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>Valenciennes</t>
+        </is>
+      </c>
+      <c r="E82" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H82" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I82" s="14" t="inlineStr">
+        <is>
+          <t>30/10/2023</t>
+        </is>
+      </c>
+      <c r="J82" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K82" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L82" s="14" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+      <c r="N82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12747</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>[FOUGERES] ARPEGE</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v/>
+      </c>
+      <c r="F83" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H83" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>26/09/2023</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-12708</t>
+        </is>
+      </c>
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="inlineStr">
+        <is>
+          <t>CD 56 MORBIHAN</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="n">
+        <v/>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G84" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H84" s="14" t="inlineStr"/>
+      <c r="I84" s="14" t="inlineStr">
+        <is>
+          <t>22/09/2023</t>
+        </is>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="K84" s="14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L84" s="14" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+      <c r="N84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
           <t>PDMDEP-11477</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr"/>
-      <c r="D80" s="14" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr"/>
+      <c r="D85" s="11" t="inlineStr">
         <is>
           <t>MONTPELLIER MMM</t>
         </is>
       </c>
-      <c r="E80" s="14" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>Déploiement Module AC</t>
         </is>
       </c>
-      <c r="F80" s="14" t="inlineStr">
+      <c r="F85" s="11" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G80" s="14" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="H80" s="14" t="inlineStr">
+      <c r="H85" s="11" t="inlineStr">
         <is>
           <t>Nouveau déploiement</t>
         </is>
       </c>
-      <c r="I80" s="14" t="inlineStr">
+      <c r="I85" s="11" t="inlineStr">
         <is>
           <t>03/09/2023</t>
         </is>
       </c>
-      <c r="J80" s="14" t="n">
+      <c r="J85" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="K80" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L80" s="14" t="inlineStr"/>
-      <c r="M80" s="14" t="inlineStr"/>
-      <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="K85" s="11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr"/>
+      <c r="N85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr"/>
-      <c r="C81" s="17" t="inlineStr"/>
-      <c r="D81" s="17" t="inlineStr"/>
-      <c r="E81" s="17" t="inlineStr"/>
-      <c r="F81" s="17" t="inlineStr"/>
-      <c r="G81" s="17" t="inlineStr"/>
-      <c r="H81" s="17" t="inlineStr"/>
-      <c r="I81" s="17" t="inlineStr"/>
-      <c r="J81" s="17" t="inlineStr"/>
-      <c r="K81" s="17" t="inlineStr"/>
-      <c r="L81" s="17" t="inlineStr"/>
-      <c r="M81" s="17" t="inlineStr"/>
-      <c r="N81" s="18" t="n">
+      <c r="B86" s="17" t="inlineStr"/>
+      <c r="C86" s="17" t="inlineStr"/>
+      <c r="D86" s="17" t="inlineStr"/>
+      <c r="E86" s="17" t="inlineStr"/>
+      <c r="F86" s="17" t="inlineStr"/>
+      <c r="G86" s="17" t="inlineStr"/>
+      <c r="H86" s="17" t="inlineStr"/>
+      <c r="I86" s="17" t="inlineStr"/>
+      <c r="J86" s="17" t="inlineStr"/>
+      <c r="K86" s="17" t="inlineStr"/>
+      <c r="L86" s="17" t="inlineStr"/>
+      <c r="M86" s="17" t="inlineStr"/>
+      <c r="N86" s="18" t="n">
         <v>47526.995</v>
       </c>
-      <c r="O81" s="18" t="n">
+      <c r="O86" s="18" t="n">
         <v>1805.22</v>
       </c>
-      <c r="P81" s="18" t="n">
-        <v>49.12</v>
+      <c r="P86" s="18" t="n">
+        <v>41.99</v>
       </c>
     </row>
   </sheetData>
@@ -6514,6 +6870,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId75"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7163,16 +7524,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>18.75</v>
+        <v>23.25</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>3.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>27.25</v>
+        <v>33.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>3.5</v>
@@ -7182,7 +7543,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
     </row>
